--- a/stories/arbres/ATOM-REL.CON.003-02.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jeanne joue dans le salon. Papa plie le linge. Noé a posé un puzzle. Les pièces sont lisses. Jeanne passe trop près. Le puzzle glisse. Les pièces roulent. Noé a les yeux mouillés. Il est triste. Maman s'approche. Maman dit : tu peux dire pardon. Jeanne dit : pardon, Noé. Maman dit : tu peux proposer un geste. Jeanne ramasse une pièce. Elle la tend. C'est un geste simple. Noé prend la pièce. Il reste un peu triste. Maman dit : la peine reste un peu. Le pardon n'efface pas tout de suite. Plus tard, dans la chambre, Jeanne apporte un verre. Une goutte tombe sur le dessin de Noé. Noé fronce les sourcils. Jeanne dit encore : pardon. Elle propose un geste. Elle apporte une feuille sèche. Noé souffle. La peine reste un peu. Au salon, puis dans la chambre, c'est pareil. On dit pardon. On propose un geste. La peine reste un peu.</t>
+          <t>Jeanne joue dans le salon. Papa plie le linge. Noé a posé un puzzle. Les pièces sont lisses. Jeanne passe trop près. Le puzzle glisse. Les pièces roulent. Noé a les yeux mouillés. Il est triste. Maman s'approche. Tu peux dire pardon. Pardon, Noé. Tu peux proposer un geste. Jeanne ramasse une pièce. Elle la tend. C'est un geste simple. Noé prend la pièce. Il reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Plus tard, dans la chambre, Jeanne apporte un verre. Une goutte tombe sur le dessin de Noé. Noé fronce les sourcils. Jeanne dit encore : pardon. Elle propose un geste. Elle apporte une feuille sèche. Noé souffle. La peine reste un peu. Au salon, puis dans la chambre, c'est pareil. On dit pardon. On propose un geste. La peine reste un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Jeanne joue dans le salon. Papa plie le linge. Noé a posé un puzzle. Les pièces sont lisses. Jeanne passe trop près. Le puzzle glisse. Les pièces roulent. Noé a les yeux mouillés. Il est triste. Maman s'approche.
+maman|Tu peux dire pardon.
+enfant-f|Pardon, Noé.
+maman|Tu peux proposer un geste.
+narrateur|Jeanne ramasse une pièce. Elle la tend. C'est un geste simple. Noé prend la pièce. Il reste un peu triste.
+maman|La peine reste un peu.
+narrateur|Le pardon n'efface pas tout de suite. Plus tard, dans la chambre, Jeanne apporte un verre. Une goutte tombe sur le dessin de Noé. Noé fronce les sourcils. Jeanne dit encore : pardon. Elle propose un geste. Elle apporte une feuille sèche. Noé souffle. La peine reste un peu. Au salon, puis dans la chambre, c'est pareil. On dit pardon. On propose un geste. La peine reste un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le puzzle de Noé a glissé. Que fait Jeanne ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Jeanne a dit pardon. Elle a proposé un geste. La peine reste un peu. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le puzzle reprend forme. Noé pose une pièce. Jeanne attend.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.003-02.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Le pardon n'efface pas tout de suite. Plus tard, dans la chambre, Jeanne apporte un verre. Une goutte tombe sur le dessin de Noé. Noé fronce les sourcils. Jeanne dit encore : pardon. Elle propose un geste. Elle apporte une feuille sèche. Noé souffle. La peine reste un peu. Au salon, puis dans la chambre, c'est pareil. On dit pardon. On propose un geste. La peine reste un peu.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Le puzzle de Noé a glissé. Que fait Jeanne ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Jeanne a dit pardon. Elle a proposé un geste. La peine reste un peu. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Le puzzle reprend forme. Noé pose une pièce. Jeanne attend.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.CON.003-02.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jeanne dit pardon deux fois</t>
+          <t>Les pièces lisses du puzzle</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mila fait glisser le puzzle d'Aniss. Elle dit pardon et tend une pièce. Plus tard, une goutte mouille son dessin. Encore pardon, encore un geste. La peine reste un peu.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jeanne joue dans le salon. Papa plie le linge. Noé a posé un puzzle. Les pièces sont lisses. Jeanne passe trop près. Le puzzle glisse. Les pièces roulent. Noé a les yeux mouillés. Il est triste. Maman s'approche. Tu peux dire pardon. Pardon, Noé. Tu peux proposer un geste. Jeanne ramasse une pièce. Elle la tend. C'est un geste simple. Noé prend la pièce. Il reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Plus tard, dans la chambre, Jeanne apporte un verre. Une goutte tombe sur le dessin de Noé. Noé fronce les sourcils. Jeanne dit encore : pardon. Elle propose un geste. Elle apporte une feuille sèche. Noé souffle. La peine reste un peu. Au salon, puis dans la chambre, c'est pareil. On dit pardon. On propose un geste. La peine reste un peu.</t>
+          <t>Le panier de linge est encore chaud. Il sent le savon doux. Papa plie une petite chaussette. La chaussette est rouge, avec un point. La pluie dessine des traits sur la vitre. Les traits glissent tout lentement. Sur la table basse, des pièces brillent. Elles sont lisses, presque froides. Une serviette tiède dépasse du panier. Elle sent encore le soleil de la lessive. Un bouton de chemise tapote le bois. Tu as vu la pluie, Mila ? Oui, maman. Elle glisse. Je plie le linge, tout près. Vous jouez doucement, d'accord ? D'accord, papa. En ce moment, Aniss pose un puzzle. Les pièces font un bateau bleu. Mila s'approche pour regarder. Le puzzle glisse. Les pièces roulent sous la table. Une pièce tapote le bois. Aniss a les yeux mouillés. Il est triste. Aniss a de la peine, Mila. Tu peux dire pardon. Pardon, Aniss. Tu peux proposer un geste. Mila ramasse une pièce lisse. Elle la tend. Je te la rends. Aniss prend la pièce. Il reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. On laisse du temps, Mila. Tu attends un peu ? Oui, papa. Aniss souffle. Il pose une pièce du bateau. Maman reste accroupie près de lui. La pièce du bateau est un peu froide. Tu peux souffler, Aniss. Aniss souffle, tout bas. Plus tard, dans la chambre, une lampe rose s'allume. Aniss a posé un dessin. Le papier sent encore le crayon. Mila apporte un verre d'eau. Une goutte tombe sur le dessin. Le bateau du papier bave un peu. Aniss fronce les sourcils. Pardon, Aniss. Je t'apporte une feuille sèche. C'est un geste. Aniss souffle encore. La peine reste un peu. Tu as dit pardon, encore. Tu as proposé un geste. Bravo, Mila. C'est du bon travail. Aniss a encore un peu de peine. C'est normal. La pluie tapote toujours la vitre. Le linge sent encore le savon.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,78 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Jeanne joue dans le salon. Papa plie le linge. Noé a posé un puzzle. Les pièces sont lisses. Jeanne passe trop près. Le puzzle glisse. Les pièces roulent. Noé a les yeux mouillés. Il est triste. Maman s'approche.
+          <t>narrateur|Le panier de linge est encore chaud.
+narrateur|Il sent le savon doux.
+narrateur|Papa plie une petite chaussette.
+narrateur|La chaussette est rouge, avec un point.
+narrateur|La pluie dessine des traits sur la vitre.
+narrateur|Les traits glissent tout lentement.
+narrateur|Sur la table basse, des pièces brillent.
+narrateur|Elles sont lisses, presque froides.
+narrateur|Une serviette tiède dépasse du panier.
+narrateur|Elle sent encore le soleil de la lessive.
+narrateur|Un bouton de chemise tapote le bois.
+maman|Tu as vu la pluie, Mila ?
+enfant-f|Oui, maman.
+enfant-f|Elle glisse.
+papa|Je plie le linge, tout près.
+papa|Vous jouez doucement, d'accord ?
+enfant-f|D'accord, papa.
+narrateur|En ce moment, Aniss pose un puzzle.
+narrateur|Les pièces font un bateau bleu.
+narrateur|Mila s'approche pour regarder.
+narrateur|Le puzzle glisse.
+narrateur|Les pièces roulent sous la table.
+narrateur|Une pièce tapote le bois.
+narrateur|Aniss a les yeux mouillés.
+narrateur|Il est triste.
+maman|Aniss a de la peine, Mila.
 maman|Tu peux dire pardon.
-enfant-f|Pardon, Noé.
+enfant-f|Pardon, Aniss.
 maman|Tu peux proposer un geste.
-narrateur|Jeanne ramasse une pièce. Elle la tend. C'est un geste simple. Noé prend la pièce. Il reste un peu triste.
+narrateur|Mila ramasse une pièce lisse.
+narrateur|Elle la tend.
+enfant-f|Je te la rends.
+narrateur|Aniss prend la pièce.
+narrateur|Il reste un peu triste.
 maman|La peine reste un peu.
-narrateur|Le pardon n'efface pas tout de suite. Plus tard, dans la chambre, Jeanne apporte un verre. Une goutte tombe sur le dessin de Noé. Noé fronce les sourcils. Jeanne dit encore : pardon. Elle propose un geste. Elle apporte une feuille sèche. Noé souffle. La peine reste un peu. Au salon, puis dans la chambre, c'est pareil. On dit pardon. On propose un geste. La peine reste un peu.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+maman|Le pardon n'efface pas tout de suite.
+papa|On laisse du temps, Mila.
+papa|Tu attends un peu ?
+enfant-f|Oui, papa.
+narrateur|Aniss souffle.
+narrateur|Il pose une pièce du bateau.
+narrateur|Maman reste accroupie près de lui.
+narrateur|La pièce du bateau est un peu froide.
+maman|Tu peux souffler, Aniss.
+narrateur|Aniss souffle, tout bas.
+narrateur|Plus tard, dans la chambre, une lampe rose s'allume.
+narrateur|Aniss a posé un dessin.
+narrateur|Le papier sent encore le crayon.
+narrateur|Mila apporte un verre d'eau.
+narrateur|Une goutte tombe sur le dessin.
+narrateur|Le bateau du papier bave un peu.
+narrateur|Aniss fronce les sourcils.
+enfant-f|Pardon, Aniss.
+enfant-f|Je t'apporte une feuille sèche.
+narrateur|C'est un geste.
+narrateur|Aniss souffle encore.
+narrateur|La peine reste un peu.
+papa|Tu as dit pardon, encore.
+papa|Tu as proposé un geste.
+maman|Bravo, Mila.
+maman|C'est du bon travail.
+maman|Aniss a encore un peu de peine.
+maman|C'est normal.
+narrateur|La pluie tapote toujours la vitre.
+narrateur|Le linge sent encore le savon.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>pluie_fenetre,linge_chaud</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1420,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le puzzle de Noé a glissé. Que fait Jeanne ?</t>
+          <t>Le puzzle d'Aniss a glissé. Que fait Mila ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1576,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le puzzle de Noé a glissé. Que fait Jeanne ?</t>
+          <t>narrateur|Le puzzle d'Aniss a glissé.
+narrateur|Que fait Mila ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1605,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jeanne a dit pardon. Elle a proposé un geste. La peine reste un peu. Papa et maman sont là.</t>
+          <t>Mila a dit pardon. Elle a proposé un geste. Elle a tendu une pièce. Bravo, Mila. C'est du bon travail. La peine d'Aniss reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1749,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Jeanne a dit pardon. Elle a proposé un geste. La peine reste un peu. Papa et maman sont là.</t>
+          <t>narrateur|Mila a dit pardon.
+narrateur|Elle a proposé un geste.
+narrateur|Elle a tendu une pièce.
+maman|Bravo, Mila.
+maman|C'est du bon travail.
+papa|La peine d'Aniss reste un peu.
+enfant-f|J'ai dit pardon.
+papa|Oui.
+papa|Et tu as attendu.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1785,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le puzzle reprend forme. Noé pose une pièce. Jeanne attend.</t>
+          <t>Le bateau du puzzle reprend forme. Aniss pose une pièce. Mila attend, les mains calmes. On reste ici un peu ? Oui, maman. La feuille sèche est près du dessin. La peine reste un peu. Je laisse du temps. Oui. C'est bien. La chaussette rouge attend dans le panier. La serviette tiède a refroidi. Le linge peut attendre. Le bateau aussi, un peu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,7 +1921,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le puzzle reprend forme. Noé pose une pièce. Jeanne attend.</t>
+          <t>narrateur|Le bateau du puzzle reprend forme.
+narrateur|Aniss pose une pièce.
+narrateur|Mila attend, les mains calmes.
+maman|On reste ici un peu ?
+enfant-f|Oui, maman.
+papa|La feuille sèche est près du dessin.
+papa|La peine reste un peu.
+enfant-f|Je laisse du temps.
+maman|Oui.
+maman|C'est bien.
+narrateur|La chaussette rouge attend dans le panier.
+narrateur|La serviette tiède a refroidi.
+papa|Le linge peut attendre.
+enfant-f|Le bateau aussi, un peu.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1866,7 +1962,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit pardon. J'ai tendu une pièce. Bravo. Tu as fait du bon travail. La pluie a presque fini. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,7 +2102,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai dit pardon.
+enfant-f|J'ai tendu une pièce.
+maman|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|La pluie a presque fini.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2028,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2167,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.003-02.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-02.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le panier de linge est encore chaud. Il sent le savon doux. Papa plie une petite chaussette. La chaussette est rouge, avec un point. La pluie dessine des traits sur la vitre. Les traits glissent tout lentement. Sur la table basse, des pièces brillent. Elles sont lisses, presque froides. Une serviette tiède dépasse du panier. Elle sent encore le soleil de la lessive. Un bouton de chemise tapote le bois. Tu as vu la pluie, Mila ? Oui, maman. Elle glisse. Je plie le linge, tout près. Vous jouez doucement, d'accord ? D'accord, papa. En ce moment, Aniss pose un puzzle. Les pièces font un bateau bleu. Mila s'approche pour regarder. Le puzzle glisse. Les pièces roulent sous la table. Une pièce tapote le bois. Aniss a les yeux mouillés. Il est triste. Aniss a de la peine, Mila. Tu peux dire pardon. Pardon, Aniss. Tu peux proposer un geste. Mila ramasse une pièce lisse. Elle la tend. Je te la rends. Aniss prend la pièce. Il reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. On laisse du temps, Mila. Tu attends un peu ? Oui, papa. Aniss souffle. Il pose une pièce du bateau. Maman reste accroupie près de lui. La pièce du bateau est un peu froide. Tu peux souffler, Aniss. Aniss souffle, tout bas. Plus tard, dans la chambre, une lampe rose s'allume. Aniss a posé un dessin. Le papier sent encore le crayon. Mila apporte un verre d'eau. Une goutte tombe sur le dessin. Le bateau du papier bave un peu. Aniss fronce les sourcils. Pardon, Aniss. Je t'apporte une feuille sèche. C'est un geste. Aniss souffle encore. La peine reste un peu. Tu as dit pardon, encore. Tu as proposé un geste. Bravo, Mila. C'est du bon travail. Aniss a encore un peu de peine. C'est normal. La pluie tapote toujours la vitre. Le linge sent encore le savon.</t>
+          <t>Le panier de linge est encore chaud. Il sent le savon doux. Papa plie une petite chaussette. La chaussette est rouge, avec un point. La pluie dessine des traits sur la vitre. Les traits glissent tout lentement. Sur la table basse, des pièces brillent. Elles sont lisses, presque froides. Une serviette tiède dépasse du panier. Elle sent encore le soleil de la lessive. Un bouton de chemise tapote le bois. Tu as vu la pluie, Mila ? Oui, maman. Elle glisse. Je plie le linge, tout près. Vous jouez doucement, d'accord ? D'accord, papa. En ce moment, Aniss pose un puzzle. Les pièces font un bateau bleu. Mila s'approche pour regarder. Le puzzle glisse. Les pièces roulent sous la table. Une pièce tapote le bois. Aniss a les yeux mouillés. Il est triste. Aniss a de la peine, Mila. Tu peux dire pardon. Pardon, Aniss. Tu peux proposer un geste. Mila ramasse une pièce lisse. Elle la tend. Je te la rends. Aniss prend la pièce. Il reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. On laisse du temps, Mila. Tu attends un peu ? Oui, papa. Aniss souffle. Il pose une pièce du bateau. Maman reste accroupie près de lui. La pièce du bateau est un peu froide. Tu peux souffler, Aniss. Aniss souffle, tout bas. Plus tard, dans la chambre, une lampe rose s'allume. Aniss a posé un dessin. Le papier sent encore le crayon. Mila apporte un verre d'eau. Une goutte tombe sur le dessin. Le bateau du papier bave un peu. Aniss fronce les sourcils. Pardon, Aniss. Je t'apporte une feuille sèche. C'est un geste. Aniss souffle encore. La peine reste un peu. Tu as dit pardon, encore. Tu as proposé un geste. Bravo, Mila. Aniss a encore un peu de peine. C'est normal. La pluie tapote toujours la vitre. Le linge sent encore le savon.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Jeanne joue dans le salon. Papa plie le linge. Noé a posé un puzzle. Les pièces sont lisses. Jeanne passe trop près. Le puzzle glisse. Les pièces roulent. Noé a les yeux mouillés. Il est triste. Maman s'approche. Maman dit : tu peux dire &lt;emphasis level="moderate"&gt;pardon&lt;/emphasis&gt;. Jeanne dit : pardon, Noé. Maman dit : tu peux proposer un geste. Jeanne ramasse une pièce. Elle la tend. C'est un geste simple. Noé prend la pièce. Il reste un peu triste. Maman dit : la peine reste un peu. Le pardon n'efface pas tout de suite. Plus tard, dans la chambre, Jeanne apporte un verre. Une goutte tombe sur le dessin de Noé. Noé fronce les sourcils. Jeanne dit encore : pardon. Elle propose un geste. Elle apporte une feuille sèche. Noé souffle. La peine reste un peu. Au salon, puis dans la chambre, c'est pareil. On dit pardon. On propose un geste. La peine reste un peu.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le panier de linge est encore chaud. Il sent le savon doux. Papa plie une petite chaussette. La chaussette est rouge, avec un point. La pluie dessine des traits sur la vitre. Les traits glissent tout lentement. Sur la table basse, des pièces brillent. Elles sont lisses, presque froides. Une serviette tiède dépasse du panier. Elle sent encore le soleil de la lessive. Un bouton de chemise tapote le bois. Tu as vu la pluie, Mila ? Oui, maman. Elle glisse. Je plie le linge, tout près. Vous jouez doucement, d'accord ? D'accord, papa. En ce moment, Aniss pose un puzzle. Les pièces font un bateau bleu. Mila s'approche pour regarder. Le puzzle glisse. Les pièces roulent sous la table. Une pièce tapote le bois. Aniss a les yeux mouillés. Il est triste. Aniss a de la peine, Mila. Tu peux dire pardon. Pardon, Aniss. Tu peux proposer un geste. Mila ramasse une pièce lisse. Elle la tend. Je te la rends. Aniss prend la pièce. Il reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. On laisse du temps, Mila. Tu attends un peu ? Oui, papa. Aniss souffle. Il pose une pièce du bateau. Maman reste accroupie près de lui. La pièce du bateau est un peu froide. Tu peux souffler, Aniss. Aniss souffle, tout bas. Plus tard, dans la chambre, une lampe rose s'allume. Aniss a posé un dessin. Le papier sent encore le crayon. Mila apporte un verre d'eau. Une goutte tombe sur le dessin. Le bateau du papier bave un peu. Aniss fronce les sourcils. Pardon, Aniss. Je t'apporte une feuille sèche. C'est un geste. Aniss souffle encore. La peine reste un peu. Tu as dit pardon, encore. Tu as proposé un geste. Bravo, Mila. Aniss a encore un peu de peine. C'est normal. La pluie tapote toujours la vitre. Le linge sent encore le savon.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1384,7 +1384,6 @@
 papa|Tu as dit pardon, encore.
 papa|Tu as proposé un geste.
 maman|Bravo, Mila.
-maman|C'est du bon travail.
 maman|Aniss a encore un peu de peine.
 maman|C'est normal.
 narrateur|La pluie tapote toujours la vitre.
@@ -1425,7 +1424,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le puzzle de Noé a glissé. Que fait Jeanne ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le puzzle d'Aniss a glissé. Que fait Mila ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1580,7 +1579,6 @@
 narrateur|Que fait Mila ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1605,12 +1603,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a dit pardon. Elle a proposé un geste. Elle a tendu une pièce. Bravo, Mila. C'est du bon travail. La peine d'Aniss reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
+          <t>Mila a dit pardon. Elle a proposé un geste. Elle a tendu une pièce. Bravo, Mila. La peine d'Aniss reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Jeanne a dit &lt;emphasis level="moderate"&gt;pardon&lt;/emphasis&gt;. Elle a proposé un geste. La peine reste un peu. Papa et maman sont là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a dit pardon. Elle a proposé un geste. Elle a tendu une pièce. Bravo, Mila. La peine d'Aniss reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1753,14 +1751,12 @@
 narrateur|Elle a proposé un geste.
 narrateur|Elle a tendu une pièce.
 maman|Bravo, Mila.
-maman|C'est du bon travail.
 papa|La peine d'Aniss reste un peu.
 enfant-f|J'ai dit pardon.
 papa|Oui.
 papa|Et tu as attendu.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1790,7 +1786,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le puzzle reprend forme. Noé pose une pièce. Jeanne attend.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le bateau du puzzle reprend forme. Aniss pose une pièce. Mila attend, les mains calmes. On reste ici un peu ? Oui, maman. La feuille sèche est près du dessin. La peine reste un peu. Je laisse du temps. Oui. C'est bien. La chaussette rouge attend dans le panier. La serviette tiède a refroidi. Le linge peut attendre. Le bateau aussi, un peu.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1937,7 +1933,6 @@
 enfant-f|Le bateau aussi, un peu.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1962,12 +1957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit pardon. J'ai tendu une pièce. Bravo. Tu as fait du bon travail. La pluie a presque fini. L'histoire est finie.</t>
+          <t>J'ai dit pardon. J'ai tendu une pièce. Bravo. La pluie a presque fini.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit pardon. J'ai tendu une pièce. Bravo. La pluie a presque fini.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2105,12 +2100,9 @@
           <t>enfant-f|J'ai dit pardon.
 enfant-f|J'ai tendu une pièce.
 maman|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|La pluie a presque fini.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La pluie a presque fini.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2129,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2174,6 +2166,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.003-02.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-02.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jeanne, Noé, papa, maman</t>
+          <t>Mila, Aniss, papa, maman</t>
         </is>
       </c>
     </row>
